--- a/kobo/gestores_semana4_diagnostico.xlsx
+++ b/kobo/gestores_semana4_diagnostico.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nome da escola</t>
+          <t>Nome do local de atuação</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Código INEP (8 dígitos; deixe em branco se não souber)</t>
+          <t>Código INEP (apenas se for local; 8 dígitos)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -912,7 +912,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A escola consegue agir? (PRI_ACTIONABILITY)</t>
+          <t>O local consegue agir? (PRI_ACTIONABILITY)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Toda a escola</t>
+          <t>Todo o local</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A escola pode agir sozinha</t>
+          <t>O local pode agir sozinho</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Está fora do alcance da escola</t>
+          <t>Está fora do alcance do local</t>
         </is>
       </c>
     </row>

--- a/kobo/gestores_semana4_diagnostico.xlsx
+++ b/kobo/gestores_semana4_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>identificacao</t>
+          <t>tcle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Identificação (igual à Semana 1)</t>
+          <t>Termo de Consentimento</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -598,25 +598,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>id_escola</t>
+          <t>tcle_texto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nome do local de atuação</t>
+          <t>TERMO DE CONSENTIMENTO LIVRE E ESCLARECIDO. Você está sendo convidado(a) a responder este Diagnóstico Socioambiental, Climático e de Educação Ambiental. A participação é voluntária: você pode recusar ou interromper a qualquer momento, sem qualquer prejuízo. As informações fornecidas, inclusive seus dados pessoais e de identificação (nome, função, local de atuação), serão tratadas com sigilo, NÃO serão compartilhadas com terceiros de forma que identifique você ou o seu local de atuação e serão utilizadas apenas para compor um banco de dados do projeto. Eventuais resultados e relatórios serão apresentados somente de forma agregada, sem identificar pessoas. O tratamento dos dados segue a Lei Geral de Proteção de Dados (Lei nº 13.709/2018). Em caso de dúvidas, procure a equipe responsável pelo projeto.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -626,58 +622,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one concordo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>id_inep</t>
+          <t>tcle_consentimento</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Código INEP (apenas se for local; 8 dígitos)</t>
+          <t>Li o termo acima e concordo em participar e em ter minhas respostas e meus dados utilizados no banco de dados do projeto, nos termos descritos.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>regex(., '^[0-9]{8}$')</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>O código INEP deve ter 8 dígitos.</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>id_nome</t>
+          <t>tcle_recusa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seu nome</t>
+          <t>Sem o seu consentimento não é possível continuar. Obrigado(a) pelo seu tempo! Você pode encerrar o formulário.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>${tcle_consentimento} = 'nao_concordo'</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -707,17 +699,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>etapa6</t>
+          <t>conteudo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Etapa 6 — Problemas e Prioridades</t>
+          <t>Diagnóstico</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>${tcle_consentimento} = 'concordo'</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>e6_nota</t>
+          <t>identificacao</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No sistema original, candidatos a problema são propostos automaticamente (ex.: "Problemas territoriais relacionados a resíduos") a partir de outras etapas e só viram problemas se confirmados. Aqui, registre cada problema confirmado (use "Adicionar" para cada um) e analise-o.</t>
+          <t>Identificação (igual à Semana 1)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -750,21 +746,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pri_problema</t>
+          <t>id_escola</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Problema confirmado (PRI_CANDIDATES / PRI_CUSTOM_PROBLEM)</t>
+          <t>Nome do local de atuação</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -779,24 +779,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pri_titulo</t>
+          <t>id_inep</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Título do problema</t>
+          <t>Código INEP (apenas se for local; 8 dígitos)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9]{8}$')</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O código INEP deve ter 8 dígitos.</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -807,22 +811,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pri_descricao</t>
+          <t>id_nome</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Descrição</t>
+          <t>Seu nome</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -830,19 +834,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one bma</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>pri_gravidade</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Gravidade (PRI_SEVERITY)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -854,17 +850,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one bma</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>pri_urgencia</t>
+          <t>etapa6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Urgência (PRI_URGENCY)</t>
+          <t>Etapa 6 — Problemas e Prioridades</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -878,17 +874,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one abrangencia</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pri_abrangencia</t>
+          <t>e6_nota</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Abrangência (PRI_REACH)</t>
+          <t>No sistema original, candidatos a problema são propostos automaticamente (ex.: "Problemas territoriais relacionados a resíduos") a partir de outras etapas e só viram problemas se confirmados. Aqui, registre cada problema confirmado (use "Adicionar" para cada um) e analise-o.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -902,17 +898,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one acionavel</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pri_acionavel</t>
+          <t>pri_problema</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>O local consegue agir? (PRI_ACTIONABILITY)</t>
+          <t>Problema confirmado (PRI_CANDIDATES / PRI_CUSTOM_PROBLEM)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -926,21 +922,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple afetados</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pri_afetados</t>
+          <t>pri_titulo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Grupos afetados (PRI_AFFECTED_GROUPS)</t>
+          <t>Título do problema</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -955,22 +955,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pri_afetados_outro</t>
+          <t>pri_descricao</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Descrição</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>selected(${pri_afetados}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -978,17 +978,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple decisao_part</t>
+          <t>select_one bma</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pri_decisao_part</t>
+          <t>pri_gravidade</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Quem deveria participar da decisão sobre este problema? (PRI_DECISION_PARTICIPANTS)</t>
+          <t>Gravidade (PRI_SEVERITY)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1002,26 +1002,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one bma</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pri_decisao_part_outro</t>
+          <t>pri_urgencia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Urgência (PRI_URGENCY)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>selected(${pri_decisao_part}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1030,27 +1026,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one abrangencia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pri_evidencias</t>
+          <t>pri_abrangencia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Evidências (PRI_EVIDENCE)</t>
+          <t>Abrangência (PRI_REACH)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -1058,11 +1050,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+          <t>select_one acionavel</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pri_acionavel</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>O local consegue agir? (PRI_ACTIONABILITY)</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1074,35 +1074,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple afetados</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pri_top_problems</t>
+          <t>pri_afetados</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Selecione até 3 prioridades (PRI_TOP_PROBLEMS) — informe os títulos dos problemas, um por linha</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>As informações acima organizam a análise, mas a escolha final não é uma soma automática de critérios — é uma decisão da comunidade escolar.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>Grupos afetados (PRI_AFFECTED_GROUPS)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -1115,22 +1103,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pri_justification</t>
+          <t>pri_afetados_outro</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Por que esta é uma prioridade agora? (PRI_JUSTIFICATION)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>selected(${pri_afetados}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -1138,27 +1126,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple decisao_part</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pri_expected_change</t>
+          <t>pri_decisao_part</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Que mudança se espera ao endereçar isso? (PRI_EXPECTED_CHANGE)</t>
+          <t>Quem deveria participar da decisão sobre este problema? (PRI_DECISION_PARTICIPANTS)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -1166,22 +1150,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_multiple decisao_part</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pri_sel_participantes</t>
+          <t>pri_decisao_part_outro</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Participantes da decisão (PRI_SELECTION_PARTICIPANTS)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>selected(${pri_decisao_part}, 'outro')</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1195,22 +1183,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pri_sel_participantes_outro</t>
+          <t>pri_evidencias</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Evidências (PRI_EVIDENCE)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>selected(${pri_sel_participantes}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -1218,19 +1206,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_one metodo_sel</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>pri_sel_metodo</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Método de seleção (PRI_SELECTION_METHOD)</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1247,22 +1227,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>pri_sel_metodo_outro</t>
+          <t>pri_top_problems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>${pri_sel_metodo}='outro'</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Selecione até 3 prioridades (PRI_TOP_PROBLEMS) — informe os títulos dos problemas, um por linha</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>As informações acima organizam a análise, mas a escolha final não é uma soma automática de critérios — é uma decisão da comunidade escolar.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -1270,15 +1258,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pri_justification</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Por que esta é uma prioridade agora? (PRI_JUSTIFICATION)</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -1286,23 +1286,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>etapa7</t>
+          <t>pri_expected_change</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Etapa 7 — Plano de Ação</t>
+          <t>Que mudança se espera ao endereçar isso? (PRI_EXPECTED_CHANGE)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -1310,17 +1314,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_multiple decisao_part</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>plano</t>
+          <t>pri_sel_participantes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano de ação (um por problema prioritário — use "Adicionar" para cada problema)</t>
+          <t>Participantes da decisão (PRI_SELECTION_PARTICIPANTS)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1339,21 +1343,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>act_problema</t>
+          <t>pri_sel_participantes_outro</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano para: título do problema confirmado</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>selected(${pri_sel_participantes}, 'outro')</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1362,27 +1366,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one metodo_sel</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>act_problem_statement</t>
+          <t>pri_sel_metodo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Enunciado do problema (ACT_PROBLEM_STATEMENT)</t>
+          <t>Método de seleção (PRI_SELECTION_METHOD)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -1395,26 +1395,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>act_evidence</t>
+          <t>pri_sel_metodo_outro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Evidências que sustentam este plano (ACT_EVIDENCE)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>${pri_sel_metodo}='outro'</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -1422,27 +1418,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>act_desired_change</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Mudança desejada (ACT_DESIRED_CHANGE)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -1450,31 +1434,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>act_objective</t>
+          <t>etapa7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Objetivo (ACT_OBJECTIVE)</t>
+          <t>Etapa 7 — Plano de Ação</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -1482,17 +1458,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>select_multiple resp_tipo</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>act_response_types</t>
+          <t>plano</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tipos de resposta (ACT_RESPONSE_TYPES)</t>
+          <t>Plano de ação (um por problema prioritário — use "Adicionar" para cada problema)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1511,21 +1487,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>act_response_types_outro</t>
+          <t>act_problema</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Plano para: título do problema confirmado</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>selected(${act_response_types}, 'outro')</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1534,23 +1510,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>atividades</t>
+          <t>act_problem_statement</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atividades (ACT_ACTIVITIES)</t>
+          <t>Enunciado do problema (ACT_PROBLEM_STATEMENT)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -1563,12 +1543,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>act_ativ_desc</t>
+          <t>act_evidence</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Descrição</t>
+          <t>Evidências que sustentam este plano (ACT_EVIDENCE)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1595,12 +1575,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>act_ativ_como</t>
+          <t>act_desired_change</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Como será implementada</t>
+          <t>Mudança desejada (ACT_DESIRED_CHANGE)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1623,18 +1603,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>act_ativ_resp</t>
+          <t>act_objective</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Responsável</t>
+          <t>Objetivo (ACT_OBJECTIVE)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -1642,17 +1630,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple resp_tipo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>act_ativ_inicio</t>
+          <t>act_response_types</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Início previsto</t>
+          <t>Tipos de resposta (ACT_RESPONSE_TYPES)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1671,17 +1659,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>act_ativ_termino</t>
+          <t>act_response_types_outro</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Término previsto</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>selected(${act_response_types}, 'outro')</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1690,17 +1682,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>select_one status_ativ</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>act_ativ_status</t>
+          <t>atividades</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Atividades (ACT_ACTIVITIES)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1714,15 +1706,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>act_ativ_desc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -1730,23 +1738,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>select_multiple publicos</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>act_audiences</t>
+          <t>act_ativ_como</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Públicos envolvidos (ACT_AUDIENCES)</t>
+          <t>Como será implementada</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -1759,21 +1771,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>act_audiences_outro</t>
+          <t>act_ativ_resp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Responsável</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>selected(${act_audiences}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1782,17 +1790,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>select_one papel_estud2</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>act_student_role</t>
+          <t>act_ativ_inicio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Papel dos estudantes (ACT_STUDENT_ROLE)</t>
+          <t>Início previsto</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1811,12 +1819,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>act_coordinator</t>
+          <t>act_ativ_termino</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Coordenador(a) (ACT_COORDINATOR)</t>
+          <t>Término previsto</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1830,27 +1838,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one status_ativ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>act_other_participants</t>
+          <t>act_ativ_status</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Outros participantes (ACT_OTHER_PARTICIPANTS)</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -1858,27 +1862,15 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>act_partners</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Parceiros (ACT_PARTNERS) — nomes dos atores mapeados na Etapa 3</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -1886,31 +1878,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple publicos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>act_partner_contribution</t>
+          <t>act_audiences</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Contribuição dos parceiros (ACT_PARTNER_CONTRIBUTION)</t>
+          <t>Públicos envolvidos (ACT_AUDIENCES)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>${act_partners} != ''</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -1923,22 +1907,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>act_resources</t>
+          <t>act_audiences_outro</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Recursos necessários (ACT_RESOURCES)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>selected(${act_audiences}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -1946,17 +1930,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>select_one viabilidade</t>
+          <t>select_one papel_estud2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>act_viability</t>
+          <t>act_student_role</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Viabilidade (ACT_VIABILITY)</t>
+          <t>Papel dos estudantes (ACT_STUDENT_ROLE)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1975,12 +1959,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>act_start</t>
+          <t>act_coordinator</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Início (ACT_START)</t>
+          <t>Coordenador(a) (ACT_COORDINATOR)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1999,18 +1983,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>act_duration</t>
+          <t>act_other_participants</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Duração (ACT_DURATION)</t>
+          <t>Outros participantes (ACT_OTHER_PARTICIPANTS)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -2018,33 +2006,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>select_multiple dependencias</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>act_dependencies</t>
+          <t>act_partners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dependências (ACT_DEPENDENCIES)</t>
+          <t>Parceiros (ACT_PARTNERS) — nomes dos atores mapeados na Etapa 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>not(selected(., 'nenhuma') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>"Nenhuma" não pode ser combinada com outras opções.</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2055,22 +2039,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>act_dependencies_outro</t>
+          <t>act_partner_contribution</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Contribuição dos parceiros (ACT_PARTNER_CONTRIBUTION)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>selected(${act_dependencies}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>${act_partners} != ''</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -2083,21 +2071,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>act_dependency_detail</t>
+          <t>act_resources</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Detalhe das dependências (ACT_DEPENDENCY_DETAIL)</t>
+          <t>Recursos necessários (ACT_RESOURCES)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>${act_dependencies} != '' and ${act_dependencies} != 'nenhuma'</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -2110,31 +2094,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one viabilidade</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>act_expected_result</t>
+          <t>act_viability</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Resultado esperado (ACT_EXPECTED_RESULT)</t>
+          <t>Viabilidade (ACT_VIABILITY)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -2142,17 +2118,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>select_multiple evid_exec</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>act_execution_evidence</t>
+          <t>act_start</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Como o resultado será evidenciado (ACT_EXECUTION_EVIDENCE)</t>
+          <t>Início (ACT_START)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2171,21 +2147,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>act_execution_evidence_outro</t>
+          <t>act_duration</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Duração (ACT_DURATION)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>selected(${act_execution_evidence}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -2194,25 +2166,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>select_multiple barr_impl</t>
+          <t>select_multiple dependencias</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>act_implementation_barriers</t>
+          <t>act_dependencies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Possíveis dificuldades de implementação (ACT_IMPLEMENTATION_BARRIERS)</t>
+          <t>Dependências (ACT_DEPENDENCIES)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nenhuma') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>"Nenhuma" não pode ser combinada com outras opções.</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -2223,7 +2203,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>act_implementation_barriers_outro</t>
+          <t>act_dependencies_outro</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2235,7 +2215,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>selected(${act_implementation_barriers}, 'outro')</t>
+          <t>selected(${act_dependencies}, 'outro')</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2251,17 +2231,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>act_mitigation</t>
+          <t>act_dependency_detail</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Como mitigar? (ACT_MITIGATION)</t>
+          <t>Detalhe das dependências (ACT_DEPENDENCY_DETAIL)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>${act_dependencies} != '' and ${act_dependencies} != 'nenhuma'</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>multiline</t>
@@ -2274,23 +2258,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>act_trilha</t>
+          <t>act_expected_result</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Trilha de coerência: problema → evidência → mudança desejada → objetivo → atividades → resultado esperado.</t>
+          <t>Resultado esperado (ACT_EXPECTED_RESULT)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -2298,17 +2290,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>select_one coerencia</t>
+          <t>select_multiple evid_exec</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>act_coherence</t>
+          <t>act_execution_evidence</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Esta cadeia é coerente? (ACT_COHERENCE_CONFIRMATION)</t>
+          <t>Como o resultado será evidenciado (ACT_EXECUTION_EVIDENCE)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2322,14 +2314,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>act_execution_evidence_outro</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>selected(${act_execution_evidence}, 'outro')</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -2338,11 +2342,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
+          <t>select_multiple barr_impl</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>act_implementation_barriers</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Possíveis dificuldades de implementação (ACT_IMPLEMENTATION_BARRIERS)</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
@@ -2350,6 +2362,158 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>act_implementation_barriers_outro</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Especifique (Outro)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>selected(${act_implementation_barriers}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>act_mitigation</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Como mitigar? (ACT_MITIGATION)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>act_trilha</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Trilha de coerência: problema → evidência → mudança desejada → objetivo → atividades → resultado esperado.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>select_one coerencia</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>act_coherence</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Esta cadeia é coerente? (ACT_COHERENCE_CONFIRMATION)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2362,7 +2526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,34 +2549,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Sim, concordo em participar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>nao_concordo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Não concordo</t>
         </is>
       </c>
     </row>
@@ -2424,46 +2588,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>abrangencia</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>individual</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>abrangencia</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>uma_turma</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uma turma</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -2475,12 +2639,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>toda_a_escola</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Todo o local</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2656,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>uma_turma</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Uma turma</t>
         </is>
       </c>
     </row>
@@ -2509,46 +2673,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>toda_a_escola</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Todo o local</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>abrangencia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>a_escola_pode_agir_sozinha</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>O local pode agir sozinho</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>abrangencia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>precisa_de_parceria</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Precisa de parceria</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2724,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>esta_fora_do_alcance_da_escola</t>
+          <t>a_escola_pode_agir_sozinha</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Está fora do alcance do local</t>
+          <t>O local pode agir sozinho</t>
         </is>
       </c>
     </row>
@@ -2577,46 +2741,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>precisa_de_parceria</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Precisa de parceria</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>afetados</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>esta_fora_do_alcance_da_escola</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Está fora do alcance do local</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>afetados</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -2628,12 +2792,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -2645,12 +2809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2826,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
@@ -2679,46 +2843,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>decisao_part</t>
+          <t>afetados</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>decisao_part</t>
+          <t>afetados</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2894,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2911,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -2764,12 +2928,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2945,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -2798,46 +2962,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>metodo_sel</t>
+          <t>decisao_part</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>votacao</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Votação</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>metodo_sel</t>
+          <t>decisao_part</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Consenso</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2849,12 +3013,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>decisao_da_gestao</t>
+          <t>votacao</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Decisão da gestão</t>
+          <t>Votação</t>
         </is>
       </c>
     </row>
@@ -2866,12 +3030,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>criterios_tecnicos</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Critérios técnicos</t>
+          <t>Consenso</t>
         </is>
       </c>
     </row>
@@ -2883,12 +3047,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>discussao_coletiva</t>
+          <t>decisao_da_gestao</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Discussão coletiva</t>
+          <t>Decisão da gestão</t>
         </is>
       </c>
     </row>
@@ -2900,46 +3064,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>criterios_tecnicos</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Critérios técnicos</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>metodo_sel</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>acao_estrutural</t>
+          <t>discussao_coletiva</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ação estrutural</t>
+          <t>Discussão coletiva</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>metodo_sel</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>acao_pedagogica</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ação pedagógica</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2951,12 +3115,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>acao_estrutural</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Ação estrutural</t>
         </is>
       </c>
     </row>
@@ -2968,12 +3132,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>comunicacao</t>
+          <t>acao_pedagogica</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Comunicação</t>
+          <t>Ação pedagógica</t>
         </is>
       </c>
     </row>
@@ -2985,12 +3149,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3166,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>monitoramento</t>
+          <t>comunicacao</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Monitoramento</t>
+          <t>Comunicação</t>
         </is>
       </c>
     </row>
@@ -3019,46 +3183,46 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>planejada</t>
+          <t>monitoramento</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Planejada</t>
+          <t>Monitoramento</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>em_andamento</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3234,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>concluida</t>
+          <t>planejada</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Planejada</t>
         </is>
       </c>
     </row>
@@ -3087,46 +3251,46 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nao_realizada</t>
+          <t>em_andamento</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Não realizada</t>
+          <t>Em andamento</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>publicos</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>concluida</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>publicos</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>nao_realizada</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Não realizada</t>
         </is>
       </c>
     </row>
@@ -3138,12 +3302,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3319,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -3172,12 +3336,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -3189,46 +3353,46 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>publicos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>publicos</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>participante</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Participante</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3404,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -3257,46 +3421,46 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>participante</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Participante</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3472,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -3325,46 +3489,46 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dependencias</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>aprovacao_da_gestao</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aprovação da gestão</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dependencias</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
@@ -3376,12 +3540,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>parceria_externa</t>
+          <t>aprovacao_da_gestao</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Parceria externa</t>
+          <t>Aprovação da gestão</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3557,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>formacao_previa</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Formação prévia</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3574,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>parceria_externa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Parceria externa</t>
         </is>
       </c>
     </row>
@@ -3427,46 +3591,46 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>formacao_previa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Formação prévia</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>evid_exec</t>
+          <t>dependencias</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>fotos</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fotos</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>evid_exec</t>
+          <t>dependencias</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>lista_de_presenca</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lista de presença</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3642,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>producao_dos_estudantes</t>
+          <t>fotos</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Produção dos estudantes</t>
+          <t>Fotos</t>
         </is>
       </c>
     </row>
@@ -3495,12 +3659,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>registro_em_ata</t>
+          <t>lista_de_presenca</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Registro em ata</t>
+          <t>Lista de presença</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3676,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>depoimentos</t>
+          <t>producao_dos_estudantes</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Depoimentos</t>
+          <t>Produção dos estudantes</t>
         </is>
       </c>
     </row>
@@ -3529,46 +3693,46 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>registro_em_ata</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Registro em ata</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>evid_exec</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>depoimentos</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Depoimentos</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>evid_exec</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3744,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Articulação</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3761,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3778,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>adesao</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Adesão</t>
+          <t>Articulação</t>
         </is>
       </c>
     </row>
@@ -3631,46 +3795,46 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Clima</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>coerente</t>
+          <t>adesao</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Coerente</t>
+          <t>Adesão</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>parcialmente_coerente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Parcialmente coerente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -3682,10 +3846,44 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>coerente</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Coerente</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>coerencia</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>parcialmente_coerente</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Parcialmente coerente</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>coerencia</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>nao_tenho_certeza</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Não tenho certeza</t>
         </is>
@@ -3755,7 +3953,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>pages</t>
+          <t>theme-grid no-text-transform</t>
         </is>
       </c>
     </row>

--- a/kobo/gestores_semana4_diagnostico.xlsx
+++ b/kobo/gestores_semana4_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2502,11 +2502,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>confirmacao</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Confirmação final</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
@@ -2514,6 +2522,90 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>confirmacao_msg</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Semana 4/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>select_one confirmo</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>confirmacao_envio</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2526,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2549,17 +2641,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>concordo</t>
+          <t>confirmo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>concordo</t>
+          <t>confirmo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sim, concordo em participar</t>
+          <t>Sim, confirmo o envio</t>
         </is>
       </c>
     </row>
@@ -2571,29 +2663,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nao_concordo</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Não concordo</t>
+          <t>Sim, concordo em participar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>nao_concordo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Não concordo</t>
         </is>
       </c>
     </row>
@@ -2605,12 +2697,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
@@ -2622,29 +2714,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>abrangencia</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>individual</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2748,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>uma_turma</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uma turma</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -2673,12 +2765,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>toda_a_escola</t>
+          <t>uma_turma</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Todo o local</t>
+          <t>Uma turma</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2782,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>toda_a_escola</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Todo o local</t>
         </is>
       </c>
     </row>
@@ -2707,29 +2799,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>abrangencia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>a_escola_pode_agir_sozinha</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>O local pode agir sozinho</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2833,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>precisa_de_parceria</t>
+          <t>a_escola_pode_agir_sozinha</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Precisa de parceria</t>
+          <t>O local pode agir sozinho</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2850,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>esta_fora_do_alcance_da_escola</t>
+          <t>precisa_de_parceria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Está fora do alcance do local</t>
+          <t>Precisa de parceria</t>
         </is>
       </c>
     </row>
@@ -2775,29 +2867,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>esta_fora_do_alcance_da_escola</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Está fora do alcance do local</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>afetados</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2901,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2918,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2935,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
@@ -2860,12 +2952,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -2877,29 +2969,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>decisao_part</t>
+          <t>afetados</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2911,12 +3003,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -2928,12 +3020,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -2945,12 +3037,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
@@ -2962,12 +3054,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -2979,12 +3071,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
@@ -2996,29 +3088,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>metodo_sel</t>
+          <t>decisao_part</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>votacao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Votação</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3122,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>votacao</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Consenso</t>
+          <t>Votação</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3139,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>decisao_da_gestao</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Decisão da gestão</t>
+          <t>Consenso</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3156,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>criterios_tecnicos</t>
+          <t>decisao_da_gestao</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Critérios técnicos</t>
+          <t>Decisão da gestão</t>
         </is>
       </c>
     </row>
@@ -3081,12 +3173,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>discussao_coletiva</t>
+          <t>criterios_tecnicos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Discussão coletiva</t>
+          <t>Critérios técnicos</t>
         </is>
       </c>
     </row>
@@ -3098,29 +3190,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>discussao_coletiva</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Discussão coletiva</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>metodo_sel</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>acao_estrutural</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ação estrutural</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3224,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>acao_pedagogica</t>
+          <t>acao_estrutural</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ação pedagógica</t>
+          <t>Ação estrutural</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3241,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>acao_pedagogica</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Ação pedagógica</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3258,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>comunicacao</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Comunicação</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3275,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>comunicacao</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Comunicação</t>
         </is>
       </c>
     </row>
@@ -3200,12 +3292,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>monitoramento</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monitoramento</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
@@ -3217,29 +3309,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>monitoramento</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Monitoramento</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>planejada</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Planejada</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3343,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>em_andamento</t>
+          <t>planejada</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Planejada</t>
         </is>
       </c>
     </row>
@@ -3268,12 +3360,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>concluida</t>
+          <t>em_andamento</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Em andamento</t>
         </is>
       </c>
     </row>
@@ -3285,29 +3377,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nao_realizada</t>
+          <t>concluida</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Não realizada</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>publicos</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>nao_realizada</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Não realizada</t>
         </is>
       </c>
     </row>
@@ -3319,12 +3411,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -3336,12 +3428,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3445,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -3370,12 +3462,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
@@ -3387,29 +3479,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>publicos</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3513,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>participante</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Participante</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3530,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>participante</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Participante</t>
         </is>
       </c>
     </row>
@@ -3455,29 +3547,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3581,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3598,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
@@ -3523,29 +3615,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dependencias</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>aprovacao_da_gestao</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aprovação da gestão</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
@@ -3557,12 +3649,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>aprovacao_da_gestao</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Aprovação da gestão</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3666,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>parceria_externa</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Parceria externa</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3683,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>formacao_previa</t>
+          <t>parceria_externa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Formação prévia</t>
+          <t>Parceria externa</t>
         </is>
       </c>
     </row>
@@ -3608,12 +3700,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>formacao_previa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Formação prévia</t>
         </is>
       </c>
     </row>
@@ -3625,29 +3717,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>evid_exec</t>
+          <t>dependencias</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>fotos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fotos</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3751,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>lista_de_presenca</t>
+          <t>fotos</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lista de presença</t>
+          <t>Fotos</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3768,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>producao_dos_estudantes</t>
+          <t>lista_de_presenca</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Produção dos estudantes</t>
+          <t>Lista de presença</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3785,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>registro_em_ata</t>
+          <t>producao_dos_estudantes</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Registro em ata</t>
+          <t>Produção dos estudantes</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3802,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>depoimentos</t>
+          <t>registro_em_ata</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Depoimentos</t>
+          <t>Registro em ata</t>
         </is>
       </c>
     </row>
@@ -3727,29 +3819,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>depoimentos</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Depoimentos</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>evid_exec</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3853,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -3778,12 +3870,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Articulação</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3887,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Articulação</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3904,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>adesao</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Adesão</t>
+          <t>Clima</t>
         </is>
       </c>
     </row>
@@ -3829,29 +3921,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>adesao</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Adesão</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>coerente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coerente</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3955,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>parcialmente_coerente</t>
+          <t>coerente</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Parcialmente coerente</t>
+          <t>Coerente</t>
         </is>
       </c>
     </row>
@@ -3880,10 +3972,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>parcialmente_coerente</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Parcialmente coerente</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>coerencia</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>nao_tenho_certeza</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Não tenho certeza</t>
         </is>

--- a/kobo/gestores_semana4_diagnostico.xlsx
+++ b/kobo/gestores_semana4_diagnostico.xlsx
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Semana 4/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir.</t>
+          <t>Semana 4/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
